--- a/dicionario_de_variaveis_final_atualizado.xlsx
+++ b/dicionario_de_variaveis_final_atualizado.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="170">
   <si>
     <t xml:space="preserve">nome original da variável</t>
   </si>
@@ -495,85 +495,34 @@
     <t xml:space="preserve">Seu plano de saúde te da direito a internações</t>
   </si>
   <si>
-    <t xml:space="preserve">Q075 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">idade_diagnostico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 Menos de 1 ano 01 a 98 Anos 99 Ignorado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade do primeiro diagnostico de asma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q076 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">crise_asma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Sim 2 Não 9  Ignorado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teve crise de asma nos últimos 6 messes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q07601 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">remedio_asma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toma algum medicamento para asma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q07704 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">remedio_semana</t>
+    <t xml:space="preserve">M01001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cigarro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usa cigarro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">domicilio_cadastrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Sim 2 Não 3 Não sabe 9  Ignorado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O seu domicílio está cadastrado na unidade de saúde da família </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q07706 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">remedio_sus</t>
   </si>
   <si>
     <t xml:space="preserve">1 Sim, todos 2 Sim, alguns 3 Não, nenhum 9  Ignorado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nas ultimas 2 semanas tomou algum medicamento para asma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q07708 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">aerossol_asma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toma algum medicamento aerossol para asma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M01001 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">cigarro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usa cigarro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B001 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">domicilio_cadastrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Sim 2 Não 3 Não sabe 9  Ignorado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O seu domicílio está cadastrado na unidade de saúde da família </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q07706 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">remedio_sus</t>
   </si>
   <si>
     <t xml:space="preserve">Algum dos medicamentos orais para asma (ou bronquite asmática) foi obtido em serviço público de saúde? </t>
@@ -604,7 +553,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -639,12 +588,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -696,24 +640,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -909,900 +857,820 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="59.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="39.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="90.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="59.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="39.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="90.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="C19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="C20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="C23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="C24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="C26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="C27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="C28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="C29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="D30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="0" t="s">
+      <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="C34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="C36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="0" t="s">
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="0" t="s">
+      <c r="D38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="D39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="C40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="4" t="s">
+      <c r="C41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="C42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="0" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="D44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="0" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="0" t="s">
+      <c r="D45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="0" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="C47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
